--- a/artfynd/A 25145-2022 artfynd.xlsx
+++ b/artfynd/A 25145-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25145-2022 artfynd.xlsx
+++ b/artfynd/A 25145-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103973664</v>
+        <v>103973655</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 25127, Helgenäs, Sm</t>
+          <t>A 25145, Helgenäs, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589701.5070516228</v>
+        <v>589735</v>
       </c>
       <c r="R2" t="n">
-        <v>6429776.29466567</v>
+        <v>6429746</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,24 +754,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ska vara A 25147!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103972140</v>
+        <v>103972018</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,7 +814,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -857,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589739.4253656517</v>
+        <v>589788</v>
       </c>
       <c r="R3" t="n">
-        <v>6429719.888854357</v>
+        <v>6429655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,19 +864,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,15 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103972094</v>
+        <v>103972050</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,7 +924,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -978,14 +937,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 25145, Sm</t>
+          <t>A 25145, Helgenäs, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589771.1366956168</v>
+        <v>589791</v>
       </c>
       <c r="R4" t="n">
-        <v>6429726.963813164</v>
+        <v>6429661</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,24 +974,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fröställning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,15 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103973691</v>
+        <v>103972094</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1108,17 +1047,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 25127, Helgenäs, Sm</t>
+          <t>A 25145, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589700.0382754996</v>
+        <v>589771</v>
       </c>
       <c r="R5" t="n">
-        <v>6429747.10262867</v>
+        <v>6429727</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1145,24 +1084,14 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ska vara A 25147!</t>
+          <t>Fröställning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,15 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103972018</v>
+        <v>103972127</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1149,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1238,14 +1162,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 25145, Helgenäs, Sm</t>
+          <t>A 25145, Helgennäs, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589788.1536692589</v>
+        <v>589763</v>
       </c>
       <c r="R6" t="n">
-        <v>6429655.242793</v>
+        <v>6429704</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,19 +1199,14 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fröställning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,50 +1234,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103973655</v>
+        <v>103972140</v>
       </c>
       <c r="B7" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1366,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589735.1254181651</v>
+        <v>589739</v>
       </c>
       <c r="R7" t="n">
-        <v>6429745.770453672</v>
+        <v>6429720</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1399,19 +1314,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1439,15 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103972127</v>
+        <v>103973647</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,11 +1372,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1487,14 +1383,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 25145, Helgennäs, Sm</t>
+          <t>A 25145, Helgenäs, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589762.6236232126</v>
+        <v>589742</v>
       </c>
       <c r="R8" t="n">
-        <v>6429703.975053843</v>
+        <v>6429734</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1524,24 +1420,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fröställning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1569,15 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103972050</v>
+        <v>103973664</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1480,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1617,14 +1493,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 25145, Helgenäs, Sm</t>
+          <t>A 25127, Helgenäs, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589791.2080572621</v>
+        <v>589702</v>
       </c>
       <c r="R9" t="n">
-        <v>6429661.143449948</v>
+        <v>6429776</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1654,19 +1530,14 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ska vara A 25147!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1694,15 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103973647</v>
+        <v>103973683</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1593,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1738,14 +1608,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 25145, Helgenäs, Sm</t>
+          <t>A 25127, Helgenäs, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589742.3011018231</v>
+        <v>589701</v>
       </c>
       <c r="R10" t="n">
-        <v>6429733.737894134</v>
+        <v>6429723</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1775,19 +1645,14 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ska vara A 25147!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1812,6 +1677,121 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>103973691</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 25127, Helgenäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>589700</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6429747</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ska vara A 25147!</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
